--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +797,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +801,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122637506</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>122637509</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +797,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +801,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +797,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +801,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 5668-2025 artfynd.xlsx
+++ b/artfynd/A 5668-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122637506</v>
+        <v>122637509</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122637509</v>
+        <v>122637506</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +797,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
